--- a/docs/beforemeetingdocs.xlsx
+++ b/docs/beforemeetingdocs.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\₩#,##0.00"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -180,6 +180,10 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="NanumGothic"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -597,7 +601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -890,6 +894,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="기본" xfId="0" builtinId="0"/>
@@ -1191,7 +1216,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="68" customHeight="1" s="72">
+    <row r="5" ht="85" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -1202,66 +1227,66 @@
           <t>기능 명세서 또는 정리된 요구사항</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E5" s="74" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="F5" s="75" t="inlineStr">
-        <is>
-          <t>발주사 제공 자료는 RFP(업무 내용) 1종. 당사가 이를 FR 26 / NFR 13 / IF 4 / OUT 8 단위로 분해한 「01 요구사항정의서」를 작성해 제출함. ※ 미팅 확인: 본 정의서를 요구사항 기준 문서로 확정할지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1" s="72">
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E5" s="101" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). RFP를 FR 26 / NFR 13 / IF 4 / OUT 8 단위로 정리함. 발주사로부터 받은 자료는 RFP 1종뿐이며, 디자인 시 기능 범위 확인용으로 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
           <t>스토리보드 또는 기획서</t>
         </is>
       </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="E6" s="76" t="inlineStr">
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="77" t="inlineStr">
-        <is>
-          <t>UI/UX 디자인이 발주사 담당(RFP 명시)이므로 디자인용 스토리보드는 본 과업 대상 아님. 다만 피팅 뷰의 화면 상태 18종(권한 거부·모델 로딩·얼굴 미검출·저조도·PD 게이팅 실패·미지원 브라우저 등)은 당사가 상태 이벤트와 사유 코드로 노출하여 발주사 디자이너가 누락 없이 화면을 그릴 수 있게 함</t>
+      <c r="F6" s="104" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일 없음] 디자인용 스토리보드·화면 기획서는 UI/UX 범위로 발주사 담당(RFP 명시). 수행사의 기술 기획서는 화면 설계를 담지 않으므로 이 행에 해당하지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00 미팅 질문지」 B-2)</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="72">
+    <row r="7" ht="34" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="32" t="inlineStr">
         <is>
           <t>로고 파일[AI]</t>
         </is>
       </c>
-      <c r="D7" s="78" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="E7" s="78" t="inlineStr">
+      <c r="D7" s="105" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="E7" s="105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="79" t="inlineStr">
-        <is>
-          <t>로고·브랜딩은 UI 범위로 과업 제외</t>
+      <c r="F7" s="106" t="inlineStr">
+        <is>
+          <t>[발주사 제공 자료] 로고·브랜딩 파일은 발주사가 제공. 수행사 준비 대상 아님</t>
         </is>
       </c>
     </row>
@@ -1692,13 +1717,16 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="46" customHeight="1" s="72">
+    <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부  |  준비되어있음 = 착수 시점(2026-09-16) 기준 자료·결정 확보 여부, 해당 없으면 "-"  |  메모의 "※ 미팅 확인" = 발주사 결정이 필요한 항목이며 docs/proposal/00-미팅질문지.md 에 결정 요청 형태로 정리함</t>
-        </is>
-      </c>
-    </row>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="30" customHeight="1" s="72">
       <c r="F30" s="37" t="n"/>
     </row>
@@ -1790,47 +1818,47 @@
           <t>기능 명세서 또는 정리된 요구사항</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E5" s="74" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="F5" s="75" t="inlineStr">
-        <is>
-          <t>발주사 제공 자료는 RFP 1종. 당사가 「01 요구사항정의서」(FR 26 / NFR 13 / IF 4 / OUT 8)를 작성해 제출함</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="68" customHeight="1" s="72">
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E5" s="101" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). 발주사로부터 받은 자료는 RFP 1종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="153" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
           <t>스토리보드 또는 기획서</t>
         </is>
       </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E6" s="76" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="F6" s="77" t="inlineStr">
-        <is>
-          <t>발주사 제공 예정 자료 없음. 당사는 PoC 설계 명세(v0.1, 2026-09-08)를 보유하고 있으나, 하이브리드 셸의 권한·오류·전체화면 상태 흐름 정의가 추가로 필요함. ※ 미팅 확인: 제공 주체·시점·형태(「00 미팅질문지」 B-2)</t>
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F6" s="104" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일 — 기획서] 「03. 기술 제안서」(docs/proposal/03-기술제안서.md), 「05. 일정·마일스톤」(docs/proposal/05-일정-마일스톤.md), PoC 개발 기획서 v0.1(docs/superpowers/specs/2026-09-08-virtual-glasses-fitting-poc-design.md). 안드로이드 WebView 하이브리드 구성과 네이티브 비교는 「03」 부록 A. 단 스토리보드(화면 흐름)는 UI/UX 범위로 발주사 담당이며 이 파일들에 포함되지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00」 B-2)</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="50" customHeight="1" s="72">
+    <row r="7" ht="51" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="38" t="inlineStr">
         <is>
@@ -1838,19 +1866,19 @@
 [PSD/Sketch/디자인 가이드/슬라이스 이미지]</t>
         </is>
       </c>
-      <c r="D7" s="78" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E7" s="78" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="F7" s="79" t="inlineStr">
-        <is>
-          <t>UI 디자인은 발주사 담당(RFP 명시). 제공 기한 10/30. 미제공 시 피팅 뷰 단독(디자인 미적용) 상태로 납품</t>
+      <c r="D7" s="105" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="E7" s="105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="106" t="inlineStr">
+        <is>
+          <t>[발주사 제공 자료] UI 디자인 파일·리소스는 발주사가 제공(RFP 명시). 수행사 준비 대상 아님. 제공 기한 10/30이며, 미제공 시 피팅 뷰 단독(디자인 미적용) 상태로 납품</t>
         </is>
       </c>
     </row>
@@ -2300,13 +2328,16 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="46" customHeight="1" s="72">
+    <row r="27" ht="62" customHeight="1" s="72">
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부  |  준비되어있음 = 착수 시점(2026-09-16) 기준 자료·결정 확보 여부, 해당 없으면 "-"  |  메모의 "※ 미팅 확인" = 발주사 결정이 필요한 항목이며 docs/proposal/00-미팅질문지.md 에 결정 요청 형태로 정리함</t>
-        </is>
-      </c>
-    </row>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="30" customHeight="1" s="72">
       <c r="F31" s="37" t="n"/>
     </row>
@@ -2398,47 +2429,47 @@
           <t>기능 명세서 또는 정리된 요구사항</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E5" s="74" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="F5" s="75" t="inlineStr">
-        <is>
-          <t>발주사 제공 자료는 RFP 1종. 당사가 「01 요구사항정의서」(FR 26 / NFR 13 / IF 4 / OUT 8)를 작성해 제출함</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1" s="72">
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E5" s="101" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). 발주사로부터 받은 자료는 RFP 1종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="153" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
           <t>스토리보드 또는 기획서</t>
         </is>
       </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E6" s="76" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="F6" s="77" t="inlineStr">
-        <is>
-          <t>발주사 제공 예정 자료 없음. 당사 PoC 설계 명세(v0.1, 2026-09-08) 보유. 피팅 뷰는 화면 1개처럼 보이나 실제 상태는 18종이어서 상태 전이 정의가 필요함. 당사가 상태 목록·사유 코드를 착수 1주 내 제공하고 발주사가 그에 맞춰 디자인하는 방식을 제안. ※ 미팅 확인(「00」 B-2)</t>
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F6" s="104" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일 — 기획서] 「03. 기술 제안서」(docs/proposal/03-기술제안서.md), 「05. 일정·마일스톤」(docs/proposal/05-일정-마일스톤.md), PoC 개발 기획서 v0.1(docs/superpowers/specs/2026-09-08-virtual-glasses-fitting-poc-design.md). 시스템 구성·공용 코어 설계·정합 엔진은 「03」 3~5장. 단 스토리보드(화면 흐름)는 UI/UX 범위로 발주사 담당이며 이 파일들에 포함되지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00」 B-2)</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="50" customHeight="1" s="72">
+    <row r="7" ht="51" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="38" t="inlineStr">
         <is>
@@ -2446,19 +2477,19 @@
 [PSD/Sketch/디자인 가이드/슬라이스 이미지]</t>
         </is>
       </c>
-      <c r="D7" s="78" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E7" s="78" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="F7" s="79" t="inlineStr">
-        <is>
-          <t>UI 디자인은 발주사 담당(RFP 명시). 제공 기한 10/30. 미제공 시 피팅 뷰 단독 상태로 납품</t>
+      <c r="D7" s="105" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="E7" s="105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="106" t="inlineStr">
+        <is>
+          <t>[발주사 제공 자료] UI 디자인 파일·리소스는 발주사가 제공(RFP 명시). 수행사 준비 대상 아님. 제공 기한 10/30이며, 미제공 시 피팅 뷰 단독 상태로 납품</t>
         </is>
       </c>
     </row>
@@ -2878,13 +2909,16 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="46" customHeight="1" s="72">
+    <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부  |  준비되어있음 = 착수 시점(2026-09-16) 기준 자료·결정 확보 여부, 해당 없으면 "-"  |  메모의 "※ 미팅 확인" = 발주사 결정이 필요한 항목이며 docs/proposal/00-미팅질문지.md 에 결정 요청 형태로 정리함</t>
-        </is>
-      </c>
-    </row>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="30" customHeight="1" s="72">
       <c r="F30" s="37" t="n"/>
     </row>
@@ -2965,7 +2999,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" s="72">
+    <row r="5" ht="102" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -2976,42 +3010,42 @@
           <t>기능 명세서 또는 정리된 요구사항</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="E5" s="74" t="inlineStr">
-        <is>
-          <t>예</t>
-        </is>
-      </c>
-      <c r="F5" s="75" t="inlineStr">
-        <is>
-          <t>당사 「01 요구사항정의서」 제출. 단 백엔드 기능 요구사항은 포함하지 않음(과업 제외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="72">
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="E5" s="101" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일 — 연동 API 한정] 제품 마스터 API 규격 docs/api/openapi.yaml(OpenAPI 3.1)과 「07. 연동 인터페이스 가이드」(docs/proposal/07-연동인터페이스가이드.md). 발주사 서버가 구현할 엔드포인트 3종 + 선택 1종을 정의함. 백엔드 자체·관리자 기능 명세는 발주사 범위로 포함하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
           <t>스토리보드 또는 기획서</t>
         </is>
       </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>아니오</t>
-        </is>
-      </c>
-      <c r="E6" s="76" t="inlineStr">
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="77" t="inlineStr">
-        <is>
-          <t>관리자 페이지가 과업 범위 밖이므로 해당 없음</t>
+      <c r="F6" s="104" t="inlineStr">
+        <is>
+          <t>[수행사 준비 파일 없음] 백엔드·관리자 기획은 과업 범위 밖으로 발주사 담당</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -3350,13 +3384,16 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1" s="72">
+    <row r="22" ht="62" customHeight="1" s="72">
       <c r="B22" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부  |  준비되어있음 = 착수 시점(2026-09-16) 기준 자료·결정 확보 여부, 해당 없으면 "-"  |  메모의 "※ 미팅 확인" = 발주사 결정이 필요한 항목이며 docs/proposal/00-미팅질문지.md 에 결정 요청 형태로 정리함</t>
-        </is>
-      </c>
-    </row>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26" ht="30" customHeight="1" s="72">
       <c r="F26" s="37" t="n"/>
     </row>

--- a/docs/beforemeetingdocs.xlsx
+++ b/docs/beforemeetingdocs.xlsx
@@ -601,7 +601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -914,6 +914,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1216,7 +1219,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="85" customHeight="1" s="72">
+    <row r="5" ht="30" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -1237,13 +1240,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F5" s="102" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). RFP를 FR 26 / NFR 13 / IF 4 / OUT 8 단위로 정리함. 발주사로부터 받은 자료는 RFP 1종뿐이며, 디자인 시 기능 범위 확인용으로 제공</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="68" customHeight="1" s="72">
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
@@ -1260,14 +1259,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일 없음] 디자인용 스토리보드·화면 기획서는 UI/UX 범위로 발주사 담당(RFP 명시). 수행사의 기술 기획서는 화면 설계를 담지 않으므로 이 행에 해당하지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00 미팅 질문지」 B-2)</t>
-        </is>
-      </c>
+      <c r="F6" s="20" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1" s="72">
+    <row r="7" ht="30" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="32" t="inlineStr">
         <is>
@@ -1284,13 +1279,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="106" t="inlineStr">
-        <is>
-          <t>[발주사 제공 자료] 로고·브랜딩 파일은 발주사가 제공. 수행사 준비 대상 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="72">
+      <c r="F7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="72">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>작업 범위 확인</t>
@@ -1311,13 +1302,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="82" t="inlineStr">
-        <is>
-          <t>디자인 과업 제외. 참고로 당사 구현 범위는 피팅 뷰 1화면 + 상태 18종 + 차단 안내 6종</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="72">
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="72">
       <c r="B9" s="24" t="n"/>
       <c r="C9" s="32" t="inlineStr">
         <is>
@@ -1334,11 +1321,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="79" t="inlineStr">
-        <is>
-          <t>디자인 과업 제외. 당사 렌더 레이아웃은 4종(PC / 모바일 세로 / 태블릿 / 가로 모드)</t>
-        </is>
-      </c>
+      <c r="F9" s="15" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1" s="72">
       <c r="B10" s="35" t="inlineStr">
@@ -1361,11 +1344,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="82" t="inlineStr">
-        <is>
-          <t>시안 작업 과업 제외</t>
-        </is>
-      </c>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1" s="72">
       <c r="B11" s="24" t="n"/>
@@ -1384,13 +1363,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="79" t="inlineStr">
-        <is>
-          <t>시안 작업 과업 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1" s="72">
+      <c r="F11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="72">
       <c r="B12" s="35" t="inlineStr">
         <is>
           <t>디자인 리소스 저작권</t>
@@ -1411,13 +1386,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="82" t="inlineStr">
-        <is>
-          <t>디자인 리소스 저작권은 발주사 관리. 당사 사용 오픈소스는 무료 라이선스만 사용</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="51" customHeight="1" s="72">
+      <c r="F12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="72">
       <c r="B13" s="28" t="inlineStr">
         <is>
           <t>[폰트/이미지/아이콘]</t>
@@ -1438,13 +1409,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="77" t="inlineStr">
-        <is>
-          <t>당사 사용 오픈소스: MediaPipe(Apache-2.0), Three.js(MIT), OpenCV.js(Apache-2.0). 고지 목록을 납품물에 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="68" customHeight="1" s="72">
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="72">
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="32" t="inlineStr">
         <is>
@@ -1461,13 +1428,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
-        <is>
-          <t>폰트·아이콘·이미지는 발주사 제공 전제. 3D 프레임 에셋(GLB)은 당사가 규격서·검수 스크립트·샘플 1종만 제공하고 상용 에셋 제작은 발주사 또는 별도 계약. ※ 미팅 확인: 3D 에셋 제작 주체와 일정(기한 10/09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1" s="72">
+      <c r="F14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="72">
       <c r="B15" s="35" t="inlineStr">
         <is>
           <t>디자인 해상도 기준 확인</t>
@@ -1488,13 +1451,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F15" s="82" t="inlineStr">
-        <is>
-          <t>반응형 구현. PC / 모바일 / 태블릿 + 가로 모드 대응. 상세는 「04 지원 브라우저·디바이스 매트릭스」 3장</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" s="72">
+      <c r="F15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="72">
       <c r="B16" s="56" t="n"/>
       <c r="C16" s="31" t="inlineStr">
         <is>
@@ -1511,13 +1470,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F16" s="77" t="inlineStr">
-        <is>
-          <t>기준 1280 x 720, 대응 범위 1024 x 768 ~ 1920 x 1080</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" s="72">
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="72">
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="31" t="inlineStr">
         <is>
@@ -1534,11 +1489,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F17" s="77" t="inlineStr">
-        <is>
-          <t>기준 390 x 844(세로), 대응 범위 360 x 640 ~ 430 x 932</t>
-        </is>
-      </c>
+      <c r="F17" s="20" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1" s="72">
       <c r="B18" s="24" t="n"/>
@@ -1557,13 +1508,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F18" s="77" t="inlineStr">
-        <is>
-          <t>기준 768 x 1024, 대응 범위 ~ 1024 x 1366</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1" s="72">
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="72">
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="32" t="inlineStr">
         <is>
@@ -1580,13 +1527,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F19" s="79" t="inlineStr">
-        <is>
-          <t>지원(레이아웃 재배치 + 카메라 종횡비 전환). 단 일정 압박 시 범위 축소 후보 1순위로 지정</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="68" customHeight="1" s="72">
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="72">
       <c r="B20" s="35" t="inlineStr">
         <is>
           <t>산출물 형태 확인</t>
@@ -1607,13 +1550,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F20" s="82" t="inlineStr">
-        <is>
-          <t>당사는 디자인 수행자가 아니므로 이 행을 "당사가 디자인을 인수받아야 하는 형태"로 해석함. 필요 형태: 화면별 시안(피그마 또는 제플린) + 슬라이스 이미지 + 컬러·타이포 가이드. ※ 미팅 확인: 제공 형태와 기한(기한 10/30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="68" customHeight="1" s="72">
+      <c r="F20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="72">
       <c r="B21" s="27" t="inlineStr">
         <is>
           <t>[PSD/이미지 슬라이싱/디자인 가이드/제플린]</t>
@@ -1634,13 +1573,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F21" s="79" t="inlineStr">
-        <is>
-          <t>당사 제공: 소스 코드 원본(Git 전체 이력), 웹 빌드 산출물, AAB/APK, API·에셋 규격서, 검수 보고서, 임베드 연동 가이드. 디자인 원본(PSD·Sketch·피그마)은 제공하지 않음. 상세는 「08 커뮤니케이션·산출물 규격」 3장</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" s="72">
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="72">
       <c r="B22" s="36" t="inlineStr">
         <is>
           <t>커뮤니케이션 방식 확인</t>
@@ -1661,13 +1596,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F22" s="82" t="inlineStr">
-        <is>
-          <t>당사 제안: GitHub Issues. ※ 미팅 확인: 발주사가 이미 쓰는 도구가 있으면 그쪽에 맞춤</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1" s="72">
+      <c r="F22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="72">
       <c r="B23" s="39" t="inlineStr">
         <is>
           <t>[트렐로/구글닥스/슬렉/이메일/카카오톡/유선/드랍박스/잔디]</t>
@@ -1688,13 +1619,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F23" s="77" t="inlineStr">
-        <is>
-          <t>GitHub Issues로 단일화 제안. 범위 변경 요청은 이 채널에 기록된 시점부터 효력 발생(구두·메신저 합의는 이슈 승격 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1" s="72">
+      <c r="F23" s="20" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="72">
       <c r="B24" s="29" t="n"/>
       <c r="C24" s="34" t="inlineStr">
         <is>
@@ -1711,16 +1638,13 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F24" s="84" t="inlineStr">
-        <is>
-          <t>일상 소통은 카카오톡 또는 슬랙, 정기 회의는 주 1회 화상. ※ 미팅 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="62" customHeight="1" s="72">
+      <c r="F24" s="22" t="n"/>
+    </row>
+    <row r="25" s="72"/>
+    <row r="26" ht="46" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1731,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="51" customHeight="1" s="72">
+    <row r="5" ht="30" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -1828,13 +1752,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F5" s="102" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). 발주사로부터 받은 자료는 RFP 1종</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="153" customHeight="1" s="72">
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
@@ -1851,14 +1771,10 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일 — 기획서] 「03. 기술 제안서」(docs/proposal/03-기술제안서.md), 「05. 일정·마일스톤」(docs/proposal/05-일정-마일스톤.md), PoC 개발 기획서 v0.1(docs/superpowers/specs/2026-09-08-virtual-glasses-fitting-poc-design.md). 안드로이드 WebView 하이브리드 구성과 네이티브 비교는 「03」 부록 A. 단 스토리보드(화면 흐름)는 UI/UX 범위로 발주사 담당이며 이 파일들에 포함되지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00」 B-2)</t>
-        </is>
-      </c>
+      <c r="F6" s="20" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1" s="72">
+    <row r="7" ht="50" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="38" t="inlineStr">
         <is>
@@ -1876,13 +1792,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="106" t="inlineStr">
-        <is>
-          <t>[발주사 제공 자료] UI 디자인 파일·리소스는 발주사가 제공(RFP 명시). 수행사 준비 대상 아님. 제공 기한 10/30이며, 미제공 시 피팅 뷰 단독(디자인 미적용) 상태로 납품</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" s="72">
+      <c r="F7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="72">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>작업 범위 확인</t>
@@ -1903,11 +1815,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F8" s="82" t="inlineStr">
-        <is>
-          <t>실질 1화면(피팅 뷰) + 상태 18종 + 차단 안내 6종. 앱 셸은 WebView 단일 액티비티</t>
-        </is>
-      </c>
+      <c r="F8" s="13" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1" s="72">
       <c r="B9" s="36" t="n"/>
@@ -1926,11 +1834,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="88" t="inlineStr">
-        <is>
-          <t>앱 내 내비게이션·메뉴는 발주사 UI 범위. 당사는 피팅 뷰 마운트/언마운트 API와 상태 이벤트만 제공</t>
-        </is>
-      </c>
+      <c r="F9" s="43" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1" s="72">
       <c r="B10" s="24" t="n"/>
@@ -1949,13 +1853,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F10" s="79" t="inlineStr">
-        <is>
-          <t>실시간 얼굴 추적(478 랜드마크), 프레임 3D 정합(스케일·회전·코 착지·클리어런스·오클루전), 간이 PD 측정, 제품 마스터 API 연동. 상세는 「01」 FR-01~FR-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="51" customHeight="1" s="72">
+      <c r="F10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="72">
       <c r="B11" s="35" t="inlineStr">
         <is>
           <t>웹 개발 구현 방식 확인</t>
@@ -1976,13 +1876,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F11" s="82" t="inlineStr">
-        <is>
-          <t>Capacitor·Cordova 등 별도 하이브리드 프레임워크를 쓰지 않고 Android WebView를 직접 구현. 의존성을 줄이고 카메라 권한·생명주기를 직접 제어하기 위함</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="102" customHeight="1" s="72">
+      <c r="F11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="72">
       <c r="B12" s="28" t="inlineStr">
         <is>
           <t>[웹앱 / 하이브리드 / 네이티브]</t>
@@ -2003,13 +1899,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F12" s="79" t="inlineStr">
-        <is>
-          <t>전면 WebView 방식. 네이티브는 카메라 권한 위임, 전체화면, 웹 자산 앱 내 번들(오프라인 기동), 생명주기(백그라운드 진입 시 카메라 정지)만 담당. Kotlin 네이티브 코어 이식은 Phase 2 별도 계약으로 분리(근거: 「03 기술제안서」 부록 A — 네이티브 병행 시 총 55~71 md로 47 영업일·1인에 불가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" s="72">
+      <c r="F12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="72">
       <c r="B13" s="35" t="inlineStr">
         <is>
           <t>기준 해상도 확인</t>
@@ -2030,11 +1922,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F13" s="82" t="inlineStr">
-        <is>
-          <t>기준 390 x 844(세로), 대응 360 x 640 ~ 430 x 932</t>
-        </is>
-      </c>
+      <c r="F13" s="13" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1" s="72">
       <c r="B14" s="24" t="n"/>
@@ -2053,11 +1941,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F14" s="77" t="inlineStr">
-        <is>
-          <t>기준 768 x 1024</t>
-        </is>
-      </c>
+      <c r="F14" s="20" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1" s="72">
       <c r="B15" s="24" t="n"/>
@@ -2076,13 +1960,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F15" s="79" t="inlineStr">
-        <is>
-          <t>지원. 일정 압박 시 범위 축소 후보 1순위</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="51" customHeight="1" s="72">
+      <c r="F15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="72">
       <c r="B16" s="57" t="inlineStr">
         <is>
           <t>개발 언어 확인</t>
@@ -2103,13 +1983,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="82" t="inlineStr">
-        <is>
-          <t>iOS 네이티브 앱은 RFP 대상 플랫폼이 아니므로 과업 제외(OUT-06). 단 웹 클라이언트가 iOS Safari 17+ 를 지원하므로 iPhone에서 브라우저로 이용 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" s="72">
+      <c r="F16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="72">
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="31" t="inlineStr">
         <is>
@@ -2126,13 +2002,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="77" t="inlineStr">
-        <is>
-          <t>Windows 클라이언트는 과업 제외. 웹 클라이언트가 Windows Chrome / Edge 94+ 를 지원함</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1" s="72">
+      <c r="F17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="72">
       <c r="B18" s="35" t="inlineStr">
         <is>
           <t>지원 범위 확인</t>
@@ -2153,13 +2025,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F18" s="82" t="inlineStr">
-        <is>
-          <t>Google Play만 해당(App Store 제외). ※ 미팅 확인: 개발자 계정 명의(발주사 명의 권장), 개인정보 처리방침 URL 제공 필요(카메라 권한 앱 필수). 기한 11/06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1" s="72">
+      <c r="F18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="72">
       <c r="B19" s="36" t="n"/>
       <c r="C19" s="31" t="inlineStr">
         <is>
@@ -2176,13 +2044,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F19" s="77" t="inlineStr">
-        <is>
-          <t>※ 미팅 확인: 기술적 사유는 당사, 정책·콘텐츠 사유는 발주사가 대응하는 분담을 제안. 심사 반려 시 2~5 md 일정 리스크</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="68" customHeight="1" s="72">
+      <c r="F19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="72">
       <c r="B20" s="36" t="n"/>
       <c r="C20" s="40" t="inlineStr">
         <is>
@@ -2199,13 +2063,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F20" s="88" t="inlineStr">
-        <is>
-          <t>※ 미팅 확인: 검수 기준이 될 중급 안드로이드 모델명을 발주사가 지정해야 함. NFR-06(중급 기기 24fps 이상) 판정 대상 기기임. 모델명만 확정되면 당사가 동급 기기를 조달. 기한 10/09</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="68" customHeight="1" s="72">
+      <c r="F20" s="43" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="72">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -2222,11 +2082,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F21" s="79" t="inlineStr">
-        <is>
-          <t>Android 10(API 29) 이상. 실제 제약은 OS가 아니라 Android System WebView 94+ 이며, 이 하한은 WebAssembly SIMD 지원 시점(Chrome 91)에서 역산한 값. 근거는 「04」 1장</t>
-        </is>
-      </c>
+      <c r="F21" s="15" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="72">
       <c r="B22" s="36" t="inlineStr">
@@ -2249,13 +2105,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F22" s="82" t="inlineStr">
-        <is>
-          <t>당사 제안: GitHub Issues. ※ 미팅 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" s="72">
+      <c r="F22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="72">
       <c r="B23" s="39" t="inlineStr">
         <is>
           <t>[트렐로/구글닥스/슬렉/이메일/카카오톡/유선/드랍박스/잔디]</t>
@@ -2276,11 +2128,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F23" s="91" t="inlineStr">
-        <is>
-          <t>GitHub Issues로 단일화. 범위 변경은 이 채널 기록 시점부터 효력 발생</t>
-        </is>
-      </c>
+      <c r="F23" s="47" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="72">
       <c r="B24" s="39" t="n"/>
@@ -2299,13 +2147,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F24" s="77" t="inlineStr">
-        <is>
-          <t>카카오톡 또는 슬랙 + 주 1회 화상 회의. ※ 미팅 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1" s="72">
+      <c r="F24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="72">
       <c r="B25" s="52" t="n"/>
       <c r="C25" s="53" t="inlineStr">
         <is>
@@ -2322,16 +2166,13 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F25" s="93" t="inlineStr">
-        <is>
-          <t>Git + GitHub 비공개 저장소. 소스 코드 원본(전체 커밋 이력 포함)이 RFP 명시 산출물이므로 저장소 자체를 이관</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="62" customHeight="1" s="72">
+      <c r="F25" s="55" t="n"/>
+    </row>
+    <row r="26" s="72"/>
+    <row r="27" ht="46" customHeight="1" s="72">
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2259,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="51" customHeight="1" s="72">
+    <row r="5" ht="30" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -2439,13 +2280,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F5" s="102" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일] 「01. 요구사항 정의서」(docs/proposal/01-요구사항정의서.md, 구글 독스 동일본). 발주사로부터 받은 자료는 RFP 1종</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="153" customHeight="1" s="72">
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
@@ -2462,14 +2299,10 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일 — 기획서] 「03. 기술 제안서」(docs/proposal/03-기술제안서.md), 「05. 일정·마일스톤」(docs/proposal/05-일정-마일스톤.md), PoC 개발 기획서 v0.1(docs/superpowers/specs/2026-09-08-virtual-glasses-fitting-poc-design.md). 시스템 구성·공용 코어 설계·정합 엔진은 「03」 3~5장. 단 스토리보드(화면 흐름)는 UI/UX 범위로 발주사 담당이며 이 파일들에 포함되지 않음. ※ 미팅 확인: 스토리보드 작성 주체·시점(「00」 B-2)</t>
-        </is>
-      </c>
+      <c r="F6" s="20" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1" s="72">
+    <row r="7" ht="50" customHeight="1" s="72">
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="38" t="inlineStr">
         <is>
@@ -2487,13 +2320,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="106" t="inlineStr">
-        <is>
-          <t>[발주사 제공 자료] UI 디자인 파일·리소스는 발주사가 제공(RFP 명시). 수행사 준비 대상 아님. 제공 기한 10/30이며, 미제공 시 피팅 뷰 단독 상태로 납품</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="85" customHeight="1" s="72">
+      <c r="F7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="72">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>HTML,CSS 작업범위 확인</t>
@@ -2514,11 +2343,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F8" s="82" t="inlineStr">
-        <is>
-          <t>피팅 뷰 1화면 + 상태 18종 + 차단 안내 6종(사유 코드 INSECURE_CONTEXT / NO_GETUSERMEDIA / NO_WEBGL2 / NO_WASM_SIMD / PERMISSION_DENIED / BROWSER_TOO_OLD). 상품 목록·장바구니 등 커머스 페이지는 범위 외</t>
-        </is>
-      </c>
+      <c r="F8" s="13" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1" s="72">
       <c r="B9" s="36" t="n"/>
@@ -2537,13 +2362,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F9" s="88" t="inlineStr">
-        <is>
-          <t>4종 — PC / 모바일 세로 / 태블릿 / 가로 모드</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" s="72">
+      <c r="F9" s="43" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="72">
       <c r="B10" s="24" t="n"/>
       <c r="C10" s="32" t="inlineStr">
         <is>
@@ -2560,13 +2381,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="79" t="inlineStr">
-        <is>
-          <t>피팅 뷰는 카메라 기반 임베드 컴포넌트라 검색 노출 대상이 아님. SEO는 이를 포함하는 발주사 커머스 페이지가 담당</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="85" customHeight="1" s="72">
+      <c r="F10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="72">
       <c r="B11" s="35" t="inlineStr">
         <is>
           <t>JavaScript 작업범위 확인</t>
@@ -2587,11 +2404,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F11" s="82" t="inlineStr">
-        <is>
-          <t>@mediapipe/tasks-vision(얼굴 추적, WASM + GPU delegate), three.js(WebGL2 렌더·GLTFLoader), OpenCV.js(ISO ID-1 카드 검출 한정, 지연 로드로 초기 로딩 영향 없음). One-Euro 필터와 정합 솔버는 자체 구현(공용 코어 2,674줄)</t>
-        </is>
-      </c>
+      <c r="F11" s="13" t="n"/>
     </row>
     <row r="12" ht="75" customHeight="1" s="72">
       <c r="B12" s="36" t="n"/>
@@ -2610,13 +2423,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F12" s="91" t="inlineStr">
-        <is>
-          <t>CSS 애니메이션이 아니라 실시간 3D 렌더 루프. requestVideoFrameCallback 기준으로 검출→정합→렌더를 한 프레임에 처리, 목표 24fps 이상. 상태 전환 페이드 300ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="85" customHeight="1" s="72">
+      <c r="F12" s="47" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="72">
       <c r="B13" s="24" t="n"/>
       <c r="C13" s="31" t="inlineStr">
         <is>
@@ -2633,13 +2442,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F13" s="77" t="inlineStr">
-        <is>
-          <t>제품 마스터 API(REST/JSON) 조회, GLB 바이너리 fetch(ETag·Cache-Control 기반 캐시), 사용자 동의 시 PD 결과 전송(수치만, 영상·랜드마크 미전송). 규격은 「07 연동 인터페이스 가이드」와 docs/api/openapi.yaml</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="119" customHeight="1" s="72">
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="44" customHeight="1" s="72">
       <c r="B14" s="56" t="n"/>
       <c r="C14" s="48" t="inlineStr">
         <is>
@@ -2657,11 +2462,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
-        <is>
-          <t>A등급(보증): Chrome 94+, Samsung Internet 17+, Edge 94+, iOS Safari 17+. B등급(동작하나 성능 미보증): Firefox. 미지원: Internet Explorer(WebGL2·WebAssembly 불가로 기술적으로 불가능). 인앱 브라우저(카카오톡·네이버·인스타그램)는 카메라 차단 사례가 많아 A등급에서 제외하고 "외부 브라우저에서 열기" 안내로 처리. 상세는 「04」 2장</t>
-        </is>
-      </c>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1" s="72">
       <c r="B15" s="35" t="inlineStr">
@@ -2684,13 +2485,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F15" s="82" t="inlineStr">
-        <is>
-          <t>반응형 + 가로 모드 지원</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" s="72">
+      <c r="F15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="72">
       <c r="B16" s="36" t="n"/>
       <c r="C16" s="44" t="inlineStr">
         <is>
@@ -2707,13 +2504,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F16" s="91" t="inlineStr">
-        <is>
-          <t>기준 1280 x 720, 대응 1024 x 768 ~ 1920 x 1080</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="68" customHeight="1" s="72">
+      <c r="F16" s="47" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="72">
       <c r="B17" s="36" t="n"/>
       <c r="C17" s="44" t="inlineStr">
         <is>
@@ -2730,11 +2523,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F17" s="91" t="inlineStr">
-        <is>
-          <t>기준 390 x 844(세로), 대응 360 x 640 ~ 430 x 932. 화면 해상도와 별개로 카메라 입력 해상도는 성능 프로파일로 분리(기준 1280 x 720, 저사양 640 x 480)</t>
-        </is>
-      </c>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1" s="72">
       <c r="B18" s="24" t="n"/>
@@ -2753,13 +2542,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F18" s="77" t="inlineStr">
-        <is>
-          <t>기준 768 x 1024, 대응 ~ 1024 x 1366</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="51" customHeight="1" s="72">
+      <c r="F18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="72">
       <c r="B19" s="35" t="inlineStr">
         <is>
           <t>산출물 형태 확인</t>
@@ -2780,13 +2565,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F19" s="82" t="inlineStr">
-        <is>
-          <t>※ 미팅 확인: 발주사 UI가 피팅 뷰를 어떤 방식으로 임베드할지(iframe / 모듈 임포트 / WebView 라우트). 당사 제안은 모듈 임포트 + 상태 이벤트 구독 API</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="68" customHeight="1" s="72">
+      <c r="F19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="72">
       <c r="B20" s="49" t="n"/>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -2803,11 +2584,7 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F20" s="77" t="inlineStr">
-        <is>
-          <t>소스 코드 원본(Git 전체 이력), 정적 빌드 산출물, 임베드 연동 가이드, 제품 마스터 API 규격(OpenAPI 3.1), 3D 에셋 규격 + 검수 스크립트, 검수 보고서. 상세는 「08」 3장</t>
-        </is>
-      </c>
+      <c r="F20" s="20" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="72">
       <c r="B21" s="36" t="inlineStr">
@@ -2830,13 +2607,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F21" s="82" t="inlineStr">
-        <is>
-          <t>당사 제안: GitHub Issues. ※ 미팅 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1" s="72">
+      <c r="F21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="72">
       <c r="B22" s="39" t="inlineStr">
         <is>
           <t>[트렐로/구글닥스/슬렉/이메일/카카오톡/유선/드랍박스/잔디]</t>
@@ -2857,11 +2630,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F22" s="91" t="inlineStr">
-        <is>
-          <t>GitHub Issues로 단일화. 범위 변경은 이 채널 기록 시점부터 효력 발생</t>
-        </is>
-      </c>
+      <c r="F22" s="47" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="72">
       <c r="B23" s="39" t="n"/>
@@ -2880,11 +2649,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F23" s="77" t="inlineStr">
-        <is>
-          <t>카카오톡 또는 슬랙 + 주 1회 화상 회의. ※ 미팅 확인</t>
-        </is>
-      </c>
+      <c r="F23" s="20" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="72">
       <c r="B24" s="29" t="n"/>
@@ -2903,16 +2668,13 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F24" s="84" t="inlineStr">
-        <is>
-          <t>Git + GitHub 비공개 저장소</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="62" customHeight="1" s="72">
+      <c r="F24" s="22" t="n"/>
+    </row>
+    <row r="25" s="72"/>
+    <row r="26" ht="46" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2761,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="102" customHeight="1" s="72">
+    <row r="5" ht="30" customHeight="1" s="72">
       <c r="B5" s="36" t="inlineStr">
         <is>
           <t>클라이언트 측 준비자료 확인</t>
@@ -3020,13 +2782,9 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F5" s="102" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일 — 연동 API 한정] 제품 마스터 API 규격 docs/api/openapi.yaml(OpenAPI 3.1)과 「07. 연동 인터페이스 가이드」(docs/proposal/07-연동인터페이스가이드.md). 발주사 서버가 구현할 엔드포인트 3종 + 선택 1종을 정의함. 백엔드 자체·관리자 기능 명세는 발주사 범위로 포함하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" s="72">
+      <c r="F5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="72">
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
@@ -3043,11 +2801,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="104" t="inlineStr">
-        <is>
-          <t>[수행사 준비 파일 없음] 백엔드·관리자 기획은 과업 범위 밖으로 발주사 담당</t>
-        </is>
-      </c>
+      <c r="F6" s="20" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
     <row r="7" ht="75" customHeight="1" s="72">
@@ -3071,13 +2825,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="82" t="inlineStr">
-        <is>
-          <t>서버 구현은 과업 제외(OUT-02). 다만 제품 마스터 API의 규격 정의와 문서 제공은 당사 과업(RFP 2-4)이며, docs/api/openapi.yaml(OpenAPI 3.1)과 「07 연동 인터페이스 가이드」로 납품함. 서버 구현은 발주사 담당</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1" s="72">
+      <c r="F7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="72">
       <c r="B8" s="50" t="n"/>
       <c r="C8" s="40" t="inlineStr">
         <is>
@@ -3094,11 +2844,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="88" t="inlineStr">
-        <is>
-          <t>서버 범위 외. 당사 클라이언트가 쓰는 오픈소스는 MediaPipe(Apache-2.0), Three.js(MIT), OpenCV.js(Apache-2.0)이며 고지 목록을 납품물에 포함</t>
-        </is>
-      </c>
+      <c r="F8" s="43" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1" s="72">
       <c r="B9" s="25" t="inlineStr">
@@ -3121,11 +2867,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="82" t="inlineStr">
-        <is>
-          <t>관리자 페이지 과업 제외</t>
-        </is>
-      </c>
+      <c r="F9" s="13" t="n"/>
     </row>
     <row r="10" ht="75" customHeight="1" s="72">
       <c r="B10" s="36" t="n"/>
@@ -3144,11 +2886,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="88" t="inlineStr">
-        <is>
-          <t>관리자 페이지 과업 제외</t>
-        </is>
-      </c>
+      <c r="F10" s="43" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1" s="72">
       <c r="B11" s="28" t="n"/>
@@ -3167,13 +2905,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="79" t="inlineStr">
-        <is>
-          <t>관리자 페이지 과업 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1" s="72">
+      <c r="F11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="72">
       <c r="B12" s="35" t="inlineStr">
         <is>
           <t>서버 개발 환경 확인</t>
@@ -3194,11 +2928,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="82" t="inlineStr">
-        <is>
-          <t>서버 개발 과업 제외. PoC 단계의 mock API는 정적 JSON 파일(public/api/v1)로 대체하며, 발주사 서버가 같은 규격으로 응답하면 클라이언트 수정 없이 연결됨</t>
-        </is>
-      </c>
+      <c r="F12" s="13" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1" s="72">
       <c r="B13" s="24" t="n"/>
@@ -3217,13 +2947,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="77" t="inlineStr">
-        <is>
-          <t>서버 개발 과업 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1" s="72">
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="72">
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="31" t="inlineStr">
         <is>
@@ -3240,13 +2966,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
-        <is>
-          <t>서버 개발 과업 제외. 클라이언트는 얼굴 영상·랜드마크를 저장하지 않으며 모든 처리는 온디바이스</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="85" customHeight="1" s="72">
+      <c r="F14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="72">
       <c r="B15" s="35" t="inlineStr">
         <is>
           <t>서버/IDC 사용위치 확인</t>
@@ -3267,11 +2989,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F15" s="97" t="inlineStr">
-        <is>
-          <t>당사 산출물은 정적 파일이므로 서버 개발은 불필요하나 HTTPS 정적 호스팅이 반드시 필요함(브라우저가 보안 컨텍스트에서만 카메라를 허용). ※ 미팅 확인: 호스팅 환경·도메인·CDN 제공 주체, CORS 허용 도메인. 기한 11/06. 미제공 시 당사 임시 호스팅으로 검수만 진행하고 운영 배포는 발주사 책임</t>
-        </is>
-      </c>
+      <c r="F15" s="107" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1" s="72">
       <c r="B16" s="28" t="inlineStr">
@@ -3305,13 +3023,9 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F17" s="82" t="inlineStr">
-        <is>
-          <t>당사 제안: GitHub Issues. ※ 미팅 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1" s="72">
+      <c r="F17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="72">
       <c r="B18" s="39" t="inlineStr">
         <is>
           <t>[트렐로/구글닥스/슬렉/이메일/카카오톡/유선/드랍박스/잔디]</t>
@@ -3332,11 +3046,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F18" s="91" t="inlineStr">
-        <is>
-          <t>GitHub Issues로 단일화. 범위 변경은 이 채널 기록 시점부터 효력 발생</t>
-        </is>
-      </c>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="72">
       <c r="B19" s="39" t="n"/>
@@ -3355,11 +3065,7 @@
           <t>아니오</t>
         </is>
       </c>
-      <c r="F19" s="77" t="inlineStr">
-        <is>
-          <t>카카오톡 또는 슬랙 + 주 1회 화상 회의. ※ 미팅 확인</t>
-        </is>
-      </c>
+      <c r="F19" s="20" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="72">
       <c r="B20" s="29" t="n"/>
@@ -3378,16 +3084,13 @@
           <t>예</t>
         </is>
       </c>
-      <c r="F20" s="84" t="inlineStr">
-        <is>
-          <t>Git + GitHub 비공개 저장소</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="62" customHeight="1" s="72">
+      <c r="F20" s="22" t="n"/>
+    </row>
+    <row r="21" s="72"/>
+    <row r="22" ht="46" customHeight="1" s="72">
       <c r="B22" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오". 메모에 파일 경로를 적음  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  "※ 미팅 확인" = 발주사 결정 필요 항목(00 미팅 질문지)</t>
+          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>

--- a/docs/beforemeetingdocs.xlsx
+++ b/docs/beforemeetingdocs.xlsx
@@ -1251,12 +1251,12 @@
       </c>
       <c r="D6" s="103" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="E6" s="103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F6" s="20" t="n"/>
@@ -1641,10 +1641,10 @@
       <c r="F24" s="22" t="n"/>
     </row>
     <row r="25" s="72"/>
-    <row r="26" ht="46" customHeight="1" s="72">
+    <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E6" s="103" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F6" s="20" t="n"/>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="D7" s="105" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="E7" s="105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
@@ -2169,10 +2169,10 @@
       <c r="F25" s="55" t="n"/>
     </row>
     <row r="26" s="72"/>
-    <row r="27" ht="46" customHeight="1" s="72">
+    <row r="27" ht="62" customHeight="1" s="72">
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E6" s="103" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F6" s="20" t="n"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="D7" s="105" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="E7" s="105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
@@ -2671,10 +2671,10 @@
       <c r="F24" s="22" t="n"/>
     </row>
     <row r="25" s="72"/>
-    <row r="26" ht="46" customHeight="1" s="72">
+    <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>
@@ -3087,10 +3087,10 @@
       <c r="F20" s="22" t="n"/>
     </row>
     <row r="21" s="72"/>
-    <row r="22" ht="46" customHeight="1" s="72">
+    <row r="22" ht="62" customHeight="1" s="72">
       <c r="B22" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  [클라이언트 측 준비자료 확인] 해당여부 = 수행사가 준비한 파일이 있으면 "예", 발주사 제공 자료이거나 준비된 파일이 없으면 "아니오"  |  [그 외 항목] 해당여부 = 본 과업(웹 클라이언트 + 안드로이드 WebView 하이브리드) 범위 해당 여부, 준비되어있음 = 착수 시점(2026-09-16) 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
         </is>
       </c>
     </row>

--- a/docs/beforemeetingdocs.xlsx
+++ b/docs/beforemeetingdocs.xlsx
@@ -1448,7 +1448,7 @@
       </c>
       <c r="E15" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F15" s="13" t="n"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E16" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F16" s="20" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E17" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F17" s="20" t="n"/>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E18" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F18" s="20" t="n"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E19" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="D20" s="80" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="E20" s="81" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="13" t="n"/>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="D21" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="E21" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
@@ -1644,7 +1644,7 @@
     <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙 (위시켓 미팅 체크리스트)  |  "클라이언트" = 요청사(발주사), "파트너" = 수행사  |  해당여부 = 본 프로젝트에 해당하는 항목인가  |  준비되어있음 = 클라이언트가 이미 준비·확정했는가 (2026-09-16 기준 받은 자료는 RFP 1종). "아니오"는 미팅에서 확인할 항목, 해당 없으면 "-"  |  메모 = 미팅에서 확인한 내용</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E8" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D11" s="80" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="E11" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E12" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E13" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F13" s="13" t="n"/>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E14" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F14" s="20" t="n"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E15" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E21" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E25" s="92" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F25" s="55" t="n"/>
@@ -2172,7 +2172,7 @@
     <row r="27" ht="62" customHeight="1" s="72">
       <c r="B27" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙 (위시켓 미팅 체크리스트)  |  "클라이언트" = 요청사(발주사), "파트너" = 수행사  |  해당여부 = 본 프로젝트에 해당하는 항목인가  |  준비되어있음 = 클라이언트가 이미 준비·확정했는가 (2026-09-16 기준 받은 자료는 RFP 1종). "아니오"는 미팅에서 확인할 항목, 해당 없으면 "-"  |  메모 = 미팅에서 확인한 내용</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="E8" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E9" s="87" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F9" s="43" t="n"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E11" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E12" s="90" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F12" s="47" t="n"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E14" s="78" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E15" s="81" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F15" s="13" t="n"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E16" s="90" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F16" s="47" t="n"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E17" s="90" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F17" s="47" t="n"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E18" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F18" s="20" t="n"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E19" s="81" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>예</t>
         </is>
       </c>
       <c r="F19" s="13" t="n"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E20" s="76" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F20" s="20" t="n"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E24" s="83" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F24" s="22" t="n"/>
@@ -2674,7 +2674,7 @@
     <row r="26" ht="62" customHeight="1" s="72">
       <c r="B26" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙 (위시켓 미팅 체크리스트)  |  "클라이언트" = 요청사(발주사), "파트너" = 수행사  |  해당여부 = 본 프로젝트에 해당하는 항목인가  |  준비되어있음 = 클라이언트가 이미 준비·확정했는가 (2026-09-16 기준 받은 자료는 RFP 1종). "아니오"는 미팅에서 확인할 항목, 해당 없으면 "-"  |  메모 = 미팅에서 확인한 내용</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E20" s="83" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니오</t>
         </is>
       </c>
       <c r="F20" s="22" t="n"/>
@@ -3090,7 +3090,7 @@
     <row r="22" ht="62" customHeight="1" s="72">
       <c r="B22" s="85" t="inlineStr">
         <is>
-          <t>※ 표기 규칙  |  이 양식의 "클라이언트"는 요청사(발주사), "파트너"는 수행사  |  [클라이언트 측 준비자료 확인] 해당여부 = 본 프로젝트에 필요한 자료인가, 준비되어있음 = 요청사가 준비해 제공했는가 (2026-09-16 기준 받은 자료는 RFP 1종)  |  [그 외 항목] 해당여부 = 본 과업 범위 해당 여부, 준비되어있음 = 착수 시점 결정·확보 여부, 해당 없으면 "-"  |  메모 열은 미팅에서 확인한 내용을 적도록 비워 둠</t>
+          <t>※ 표기 규칙 (위시켓 미팅 체크리스트)  |  "클라이언트" = 요청사(발주사), "파트너" = 수행사  |  해당여부 = 본 프로젝트에 해당하는 항목인가  |  준비되어있음 = 클라이언트가 이미 준비·확정했는가 (2026-09-16 기준 받은 자료는 RFP 1종). "아니오"는 미팅에서 확인할 항목, 해당 없으면 "-"  |  메모 = 미팅에서 확인한 내용</t>
         </is>
       </c>
     </row>
